--- a/src/database/diff_cases_npi.xlsx
+++ b/src/database/diff_cases_npi.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Repositories\XpressCredentialling\src\database\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776D55D2-2C4D-48DA-8479-81946288320F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABEA1360-9C7B-4E0B-8123-70A5FD4C81B3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -273,18 +273,12 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -319,7 +313,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -604,6 +598,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="18.109375" customWidth="1"/>
+    <col min="13" max="13" width="24.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.3">
